--- a/exercisemenu-workout-plans/ExerciseMenu_Workout_Plans_YMYL_Safe_Roadmap.xlsx
+++ b/exercisemenu-workout-plans/ExerciseMenu_Workout_Plans_YMYL_Safe_Roadmap.xlsx
@@ -1992,7 +1992,7 @@
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>To write</t>
+          <t>Written (Batch 3)</t>
         </is>
       </c>
       <c r="L27" s="8" t="n"/>
